--- a/action/actionList_protocolCore.xlsx
+++ b/action/actionList_protocolCore.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcorbara\Documents\ArgoX3_API_Mobile_CORE\action\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{827C7D49-7C12-4AC9-8219-9655C3C29D0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E67BFB-BBB8-4E13-8928-48FF61B1DA30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6885" yWindow="3465" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="25">
   <si>
     <t>Descrizione</t>
   </si>
@@ -91,6 +91,15 @@
   </si>
   <si>
     <t>YAX3C</t>
+  </si>
+  <si>
+    <t>Codice Tipo per Patch</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ACT</t>
+  </si>
+  <si>
+    <t>ACT</t>
   </si>
 </sst>
 </file>
@@ -122,7 +131,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -152,28 +161,6 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -189,7 +176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -203,11 +190,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -489,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" customWidth="1"/>
@@ -502,44 +486,48 @@
     <col min="8" max="8" width="12.85546875" customWidth="1"/>
     <col min="9" max="9" width="25.5703125" customWidth="1"/>
     <col min="10" max="10" width="12.85546875" customWidth="1"/>
+    <col min="12" max="12" width="26.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="L1" s="4" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -573,8 +561,11 @@
       <c r="K2" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="L2" s="5" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>19</v>
       </c>
@@ -607,6 +598,9 @@
       </c>
       <c r="K3" s="3" t="s">
         <v>17</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
